--- a/data/trans_bre/P2A_psíq_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P2A_psíq_R-Estudios-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 0,64</t>
+          <t>-1,52; 0,68</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 1,01</t>
+          <t>-2,08; 1,24</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 1,91</t>
+          <t>-0,82; 1,88</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 1,77</t>
+          <t>-1,97; 1,7</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-59,36; 48,72</t>
+          <t>-58,08; 54,37</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-46,37; 44,91</t>
+          <t>-47,32; 51,46</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-32,43; 162,19</t>
+          <t>-32,51; 159,6</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-33,29; 65,7</t>
+          <t>-38,63; 59,67</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 0,71</t>
+          <t>-0,4; 0,73</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 1,06</t>
+          <t>-0,44; 1,09</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 1,31</t>
+          <t>-0,05; 1,39</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,63; 34,28</t>
+          <t>0,62; 31,53</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-54,05; 299,61</t>
+          <t>-56,75; 260,99</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-29,33; 122,8</t>
+          <t>-29,36; 122,51</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-6,47; 273,5</t>
+          <t>-9,96; 284,32</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>28,59; 2661,17</t>
+          <t>34,75; 2539,44</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,45; 2,73</t>
+          <t>0,39; 2,91</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 2,12</t>
+          <t>-1,34; 2,29</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 1,54</t>
+          <t>-0,21; 1,57</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 1,92</t>
+          <t>-1,74; 1,55</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -885,17 +885,17 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-70,19; 432,24</t>
+          <t>-71,74; 443,16</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-81,77; —</t>
+          <t>-86,39; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-49,81; 148,67</t>
+          <t>-58,37; 114,86</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 0,77</t>
+          <t>-0,26; 0,76</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 0,95</t>
+          <t>-0,44; 0,98</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,25</t>
+          <t>0,1; 1,24</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,5; 23,42</t>
+          <t>0,47; 23,07</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-23,18; 109,91</t>
+          <t>-23,31; 118,21</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-22,84; 62,99</t>
+          <t>-20,89; 67,07</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,2; 172,84</t>
+          <t>8,0; 161,34</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>23,38; 1252,75</t>
+          <t>20,77; 1232,68</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2A_psíq_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P2A_psíq_R-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,12</t>
+          <t>0,06</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>1,6%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 0,68</t>
+          <t>-1,5; 0,71</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 1,24</t>
+          <t>-2,19; 1,01</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 1,88</t>
+          <t>-0,73; 1,95</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 1,7</t>
+          <t>-1,88; 1,75</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-58,08; 54,37</t>
+          <t>-56,57; 59,36</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-47,32; 51,46</t>
+          <t>-49,68; 44,46</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-32,51; 159,6</t>
+          <t>-28,82; 161,57</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-38,63; 59,67</t>
+          <t>-34,84; 66,33</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9,83</t>
+          <t>1,03</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>576,17%</t>
+          <t>54,14%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 0,73</t>
+          <t>-0,33; 0,84</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 1,09</t>
+          <t>-0,43; 1,17</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 1,39</t>
+          <t>-0,06; 1,4</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,62; 31,53</t>
+          <t>0,14; 2,04</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-56,75; 260,99</t>
+          <t>-51,07; 392,18</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-29,36; 122,51</t>
+          <t>-29,39; 127,42</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-9,96; 284,32</t>
+          <t>-9,34; 290,59</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>34,75; 2539,44</t>
+          <t>4,07; 131,85</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,08</t>
+          <t>-0,02</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>-1,0%</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,39; 2,91</t>
+          <t>0,5; 3,08</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 2,29</t>
+          <t>-1,39; 2,29</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 1,57</t>
+          <t>-0,34; 1,61</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 1,55</t>
+          <t>-1,72; 1,4</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -885,17 +885,17 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-71,74; 443,16</t>
+          <t>-71,81; 491,76</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-86,39; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-58,37; 114,86</t>
+          <t>-51,51; 107,22</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6,18</t>
+          <t>0,72</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>292,22%</t>
+          <t>31,31%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 0,76</t>
+          <t>-0,26; 0,78</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 0,98</t>
+          <t>-0,49; 0,92</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,1; 1,24</t>
+          <t>0,15; 1,3</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,47; 23,07</t>
+          <t>-0,01; 1,47</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-23,31; 118,21</t>
+          <t>-26,02; 112,17</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-20,89; 67,07</t>
+          <t>-22,97; 64,58</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,0; 161,34</t>
+          <t>9,3; 178,72</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>20,77; 1232,68</t>
+          <t>-1,15; 76,16</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2A_psíq_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P2A_psíq_R-Estudios-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con limitación por discapacidad psíquica</t>
+          <t>Población que convive con personas con alguna limitación por discapacidad psíquica</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
